--- a/logs/unmatched_ports.xlsx
+++ b/logs/unmatched_ports.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,145 +515,89 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>At Zhoushan East Anchorage</t>
+          <t>At Zhoushan Xiazhimen K</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>At Zhoushan North Anchorag</t>
+          <t>At Zhoushan West Anchora</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhimen S</t>
+          <t>At Liuheng North Anchorage</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhimen K</t>
+          <t>At Liuheng North Anchorag</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>At Zhoushan West Anchora</t>
+          <t>At Zhoushan Xiazhime K</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>At Liuheng North Anchorage</t>
+          <t>At Zhoushan West Anch</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>At Liuheng North Anchorag</t>
+          <t xml:space="preserve">At Zhoushan Xiazhimen </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhime K</t>
+          <t>At Zhoushan Xiazhime</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>At Zhoushan West Anch</t>
+          <t>At Zhoushan Xiazhimen</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">At Zhoushan Xiazhimen </t>
+          <t>At Liuheng North Ancho</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhime</t>
+          <t>At Zhoushan Xiazhimen N</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhimen</t>
+          <t>At Zhoushan Xiazhim</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
-        <is>
-          <t>At Liuheng North Ancho</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>At Zhoushan Xiazhimen N</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>At Zhoushan East Ancho</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>At Zhoushan Qushan Bun</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">At Zhoushan Xiazhime South </t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>At Zhoushan Xiazhim</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>At Zhoushan North Anc</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>At Zhoushan East Anch</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
         <is>
           <t>At Zhoushan West Anchorag</t>
         </is>

--- a/logs/unmatched_ports.xlsx
+++ b/logs/unmatched_ports.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,145 +515,89 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>At Zhoushan East Anchorage</t>
+          <t>At Zhoushan Xiazhimen K</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>At Zhoushan North Anchorag</t>
+          <t>At Zhoushan West Anchora</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhimen S</t>
+          <t>At Liuheng North Anchorage</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhimen K</t>
+          <t>At Liuheng North Anchorag</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>At Zhoushan West Anchora</t>
+          <t>At Zhoushan Xiazhime K</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>At Liuheng North Anchorage</t>
+          <t>At Zhoushan West Anch</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>At Liuheng North Anchorag</t>
+          <t xml:space="preserve">At Zhoushan Xiazhimen </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhime K</t>
+          <t>At Zhoushan Xiazhime</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>At Zhoushan West Anch</t>
+          <t>At Zhoushan Xiazhimen</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">At Zhoushan Xiazhimen </t>
+          <t>At Liuheng North Ancho</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhime</t>
+          <t>At Zhoushan Xiazhimen N</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>At Zhoushan Xiazhimen</t>
+          <t>At Zhoushan Xiazhim</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
-        <is>
-          <t>At Liuheng North Ancho</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>At Zhoushan Xiazhimen N</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>At Zhoushan East Ancho</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>At Zhoushan Qushan Bun</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">At Zhoushan Xiazhime South </t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>At Zhoushan Xiazhim</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>At Zhoushan North Anc</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>At Zhoushan East Anch</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
         <is>
           <t>At Zhoushan West Anchorag</t>
         </is>
